--- a/Excel/BattleSummonConfig.xlsx
+++ b/Excel/BattleSummonConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26626"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E591B8F2-C43A-4EBE-9518-48B75CAB39F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9EB18B3-3882-4E37-BCF8-96B62F7B55B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BattleSummonProto" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
     <author>Admin</author>
   </authors>
   <commentList>
-    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{FAA19F49-198C-4871-BB92-9527508A113E}">
+    <comment ref="G3" authorId="0" shapeId="0" xr:uid="{FAA19F49-198C-4871-BB92-9527508A113E}">
       <text>
         <r>
           <rPr>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="43">
   <si>
     <t>Id</t>
   </si>
@@ -193,6 +193,26 @@
   </si>
   <si>
     <t>SceneId</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemName_EN</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Recruit Soldiers</t>
+  </si>
+  <si>
+    <t>Recruit a group of soldiers</t>
+  </si>
+  <si>
+    <t>Recruit the strongman</t>
+  </si>
+  <si>
+    <t>Recruit the Two-headed Dragon</t>
+  </si>
+  <si>
+    <t>c</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -1374,7 +1394,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1401,6 +1421,7 @@
     <xf numFmtId="3" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="314">
     <cellStyle name="20% - 强调文字颜色 1 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
@@ -2044,18 +2065,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C1:J39"/>
+  <dimension ref="C1:K39"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="5" width="26.125" customWidth="1"/>
-    <col min="6" max="6" width="30.625" customWidth="1"/>
-    <col min="7" max="8" width="18.375" customWidth="1"/>
-    <col min="9" max="10" width="21.5" customWidth="1"/>
+    <col min="4" max="6" width="26.125" customWidth="1"/>
+    <col min="7" max="7" width="30.625" customWidth="1"/>
+    <col min="8" max="9" width="18.375" customWidth="1"/>
+    <col min="10" max="11" width="21.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:10" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="3:11" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="E2" s="10" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
@@ -2063,25 +2089,28 @@
         <v>9</v>
       </c>
       <c r="E3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="H3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="I3" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="J3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="K3" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C4" s="3" t="s">
         <v>0</v>
       </c>
@@ -2089,25 +2118,28 @@
         <v>5</v>
       </c>
       <c r="E4" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="G4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="H4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="I4" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="J4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="K4" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C5" s="3" t="s">
         <v>1</v>
       </c>
@@ -2115,13 +2147,13 @@
         <v>4</v>
       </c>
       <c r="E5" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="G5" s="6" t="s">
         <v>8</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>13</v>
       </c>
       <c r="H5" s="6" t="s">
         <v>13</v>
@@ -2132,216 +2164,243 @@
       <c r="J5" s="6" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="6" spans="3:10" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K5" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C6" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" s="8">
         <v>3000001</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="G6" s="9" t="s">
         <v>27</v>
-      </c>
-      <c r="G6" s="9">
-        <v>1</v>
       </c>
       <c r="H6" s="9">
         <v>1</v>
       </c>
-      <c r="I6" s="8">
+      <c r="I6" s="9">
+        <v>1</v>
+      </c>
+      <c r="J6" s="8">
         <v>10000</v>
       </c>
-      <c r="J6" s="8">
+      <c r="K6" s="8">
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="3:10" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C7" s="7" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" s="8">
         <v>3000001</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="G7" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="G7" s="9">
+      <c r="H7" s="9">
         <v>6</v>
       </c>
-      <c r="H7" s="9">
+      <c r="I7" s="9">
         <v>1</v>
       </c>
-      <c r="I7" s="8">
+      <c r="J7" s="8">
         <v>50000</v>
       </c>
-      <c r="J7" s="8">
+      <c r="K7" s="8">
         <v>120</v>
       </c>
     </row>
-    <row r="8" spans="3:10" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C8" s="7" t="s">
         <v>19</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F8" s="8">
         <v>3000001</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="G8" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="G8" s="9">
+      <c r="H8" s="9">
         <v>1</v>
       </c>
-      <c r="H8" s="9">
+      <c r="I8" s="9">
         <v>5</v>
       </c>
-      <c r="I8" s="8">
+      <c r="J8" s="8">
         <v>300000</v>
       </c>
-      <c r="J8" s="8">
+      <c r="K8" s="8">
         <v>300</v>
       </c>
     </row>
-    <row r="9" spans="3:10" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C9" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9" s="8">
         <v>3000001</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="G9" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="G9" s="9">
+      <c r="H9" s="9">
         <v>1</v>
       </c>
-      <c r="H9" s="9">
+      <c r="I9" s="9">
         <v>10</v>
       </c>
-      <c r="I9" s="8">
+      <c r="J9" s="8">
         <v>500000</v>
       </c>
-      <c r="J9" s="8">
+      <c r="K9" s="8">
         <v>600</v>
       </c>
     </row>
-    <row r="10" spans="3:10" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C10" s="7" t="s">
         <v>31</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="E10" s="8">
+      <c r="E10" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F10" s="8">
         <v>3000002</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="G10" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="G10" s="9">
-        <v>1</v>
       </c>
       <c r="H10" s="9">
         <v>1</v>
       </c>
-      <c r="I10" s="8">
+      <c r="I10" s="9">
+        <v>1</v>
+      </c>
+      <c r="J10" s="8">
         <v>10000</v>
       </c>
-      <c r="J10" s="8">
+      <c r="K10" s="8">
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="3:10" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C11" s="7" t="s">
         <v>32</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="E11" s="8">
+      <c r="E11" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="F11" s="8">
         <v>3000002</v>
       </c>
-      <c r="F11" s="9" t="s">
+      <c r="G11" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="G11" s="9">
+      <c r="H11" s="9">
         <v>6</v>
       </c>
-      <c r="H11" s="9">
+      <c r="I11" s="9">
         <v>1</v>
       </c>
-      <c r="I11" s="8">
+      <c r="J11" s="8">
         <v>50000</v>
       </c>
-      <c r="J11" s="8">
+      <c r="K11" s="8">
         <v>120</v>
       </c>
     </row>
-    <row r="12" spans="3:10" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C12" s="7" t="s">
         <v>33</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="E12" s="8">
+      <c r="E12" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F12" s="8">
         <v>3000002</v>
       </c>
-      <c r="F12" s="9" t="s">
+      <c r="G12" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="G12" s="9">
+      <c r="H12" s="9">
         <v>1</v>
       </c>
-      <c r="H12" s="9">
+      <c r="I12" s="9">
         <v>5</v>
       </c>
-      <c r="I12" s="8">
+      <c r="J12" s="8">
         <v>300000</v>
       </c>
-      <c r="J12" s="8">
+      <c r="K12" s="8">
         <v>300</v>
       </c>
     </row>
-    <row r="13" spans="3:10" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C13" s="7" t="s">
         <v>34</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E13" s="8">
+      <c r="E13" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F13" s="8">
         <v>3000002</v>
       </c>
-      <c r="F13" s="9" t="s">
+      <c r="G13" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="G13" s="9">
+      <c r="H13" s="9">
         <v>1</v>
       </c>
-      <c r="H13" s="9">
+      <c r="I13" s="9">
         <v>10</v>
       </c>
-      <c r="I13" s="8">
+      <c r="J13" s="8">
         <v>500000</v>
       </c>
-      <c r="J13" s="8">
+      <c r="K13" s="8">
         <v>600</v>
       </c>
     </row>
-    <row r="14" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
@@ -2350,8 +2409,9 @@
       <c r="H14" s="5"/>
       <c r="I14" s="5"/>
       <c r="J14" s="5"/>
-    </row>
-    <row r="15" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K14" s="5"/>
+    </row>
+    <row r="15" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
@@ -2360,8 +2420,9 @@
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
       <c r="J15" s="5"/>
-    </row>
-    <row r="16" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K15" s="5"/>
+    </row>
+    <row r="16" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
@@ -2370,8 +2431,9 @@
       <c r="H16" s="5"/>
       <c r="I16" s="5"/>
       <c r="J16" s="5"/>
-    </row>
-    <row r="17" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K16" s="5"/>
+    </row>
+    <row r="17" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
@@ -2380,8 +2442,9 @@
       <c r="H17" s="5"/>
       <c r="I17" s="5"/>
       <c r="J17" s="5"/>
-    </row>
-    <row r="18" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K17" s="5"/>
+    </row>
+    <row r="18" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
@@ -2390,8 +2453,9 @@
       <c r="H18" s="5"/>
       <c r="I18" s="5"/>
       <c r="J18" s="5"/>
-    </row>
-    <row r="19" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K18" s="5"/>
+    </row>
+    <row r="19" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
@@ -2400,8 +2464,9 @@
       <c r="H19" s="5"/>
       <c r="I19" s="5"/>
       <c r="J19" s="5"/>
-    </row>
-    <row r="20" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K19" s="5"/>
+    </row>
+    <row r="20" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
@@ -2410,8 +2475,9 @@
       <c r="H20" s="5"/>
       <c r="I20" s="5"/>
       <c r="J20" s="5"/>
-    </row>
-    <row r="21" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K20" s="5"/>
+    </row>
+    <row r="21" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C21" s="5"/>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -2420,8 +2486,9 @@
       <c r="H21" s="5"/>
       <c r="I21" s="5"/>
       <c r="J21" s="5"/>
-    </row>
-    <row r="22" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K21" s="5"/>
+    </row>
+    <row r="22" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C22" s="5"/>
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
@@ -2430,8 +2497,9 @@
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
       <c r="J22" s="5"/>
-    </row>
-    <row r="23" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K22" s="5"/>
+    </row>
+    <row r="23" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C23" s="5"/>
       <c r="D23" s="5"/>
       <c r="E23" s="5"/>
@@ -2440,8 +2508,9 @@
       <c r="H23" s="5"/>
       <c r="I23" s="5"/>
       <c r="J23" s="5"/>
-    </row>
-    <row r="24" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K23" s="5"/>
+    </row>
+    <row r="24" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C24" s="5"/>
       <c r="D24" s="5"/>
       <c r="E24" s="5"/>
@@ -2450,8 +2519,9 @@
       <c r="H24" s="5"/>
       <c r="I24" s="5"/>
       <c r="J24" s="5"/>
-    </row>
-    <row r="25" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K24" s="5"/>
+    </row>
+    <row r="25" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C25" s="5"/>
       <c r="D25" s="5"/>
       <c r="E25" s="5"/>
@@ -2460,8 +2530,9 @@
       <c r="H25" s="5"/>
       <c r="I25" s="5"/>
       <c r="J25" s="5"/>
-    </row>
-    <row r="26" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K25" s="5"/>
+    </row>
+    <row r="26" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C26" s="5"/>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
@@ -2470,8 +2541,9 @@
       <c r="H26" s="5"/>
       <c r="I26" s="5"/>
       <c r="J26" s="5"/>
-    </row>
-    <row r="27" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K26" s="5"/>
+    </row>
+    <row r="27" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C27" s="5"/>
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
@@ -2480,8 +2552,9 @@
       <c r="H27" s="5"/>
       <c r="I27" s="5"/>
       <c r="J27" s="5"/>
-    </row>
-    <row r="28" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K27" s="5"/>
+    </row>
+    <row r="28" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C28" s="5"/>
       <c r="D28" s="5"/>
       <c r="E28" s="5"/>
@@ -2490,8 +2563,9 @@
       <c r="H28" s="5"/>
       <c r="I28" s="5"/>
       <c r="J28" s="5"/>
-    </row>
-    <row r="29" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K28" s="5"/>
+    </row>
+    <row r="29" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
       <c r="E29" s="4"/>
@@ -2500,10 +2574,11 @@
       <c r="H29" s="4"/>
       <c r="I29" s="4"/>
       <c r="J29" s="4"/>
-    </row>
-    <row r="30" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="31" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="32" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+      <c r="K29" s="4"/>
+    </row>
+    <row r="30" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="31" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="32" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="33" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
